--- a/erp-server/erp-server-oms/src/main/resources/excel/SoPriceDetail.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoPriceDetail.xlsx
@@ -54,6 +54,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -69,6 +76,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -106,6 +120,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -121,6 +142,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -136,7 +164,7 @@
   </si>
   <si>
     <r>
-      <t>*</t>
+      <t>*失</t>
     </r>
     <r>
       <rPr>
@@ -145,7 +173,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>生效时间</t>
+      <t>效时间</t>
     </r>
   </si>
 </sst>
@@ -159,17 +187,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -323,13 +344,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -672,143 +686,140 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1188,10 +1199,10 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
